--- a/files/九龙-启德-柏蔚森 III.xlsx
+++ b/files/九龙-启德-柏蔚森 III.xlsx
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>9391000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>24520</v>
+        <v>24584</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>9391000</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>24520</v>
+        <v>24584</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>6959000</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>18170</v>
+        <v>18217</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>6959000</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>18170</v>
+        <v>18217</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
@@ -10438,38 +10438,30 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H155" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I155" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="n">
+        <v>9134000</v>
+      </c>
+      <c r="I155" s="5" t="n">
+        <v>23911</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K155" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L155" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K155" s="5" t="n">
+        <v>9134000</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>23911</v>
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
@@ -10478,7 +10470,7 @@
       </c>
       <c r="N155" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -17443,7 +17435,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -17453,7 +17445,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>231</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -17854,9 +17846,9 @@
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t>E | 383呎 (2房)
+          <t>E | 382呎 (2房)
 $939万
-$24,520/呎
+$24,584/呎
 (26年-06月-03日)</t>
         </is>
       </c>
@@ -18709,9 +18701,9 @@
       </c>
       <c r="F17" s="22" t="inlineStr">
         <is>
-          <t>E | 383呎 (2房)
+          <t>E | 382呎 (2房)
 $696万
-$18,170/呎
+$18,217/呎
 (24年-10月-23日)</t>
         </is>
       </c>
@@ -18778,12 +18770,12 @@
 (25年-09月-09日)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 382呎 (2房)
-招标单位
--
-(在售)</t>
+$913万
+$23,911/呎
+(26年-09月-05日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">

--- a/files/九龙-启德-柏蔚森 III.xlsx
+++ b/files/九龙-启德-柏蔚森 III.xlsx
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>8851000</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>23110</v>
+        <v>23170</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>8851000</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>23110</v>
+        <v>23170</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
@@ -18036,9 +18036,9 @@
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t>E | 383呎 (2房)
+          <t>E | 382呎 (2房)
 $885万
-$23,110/呎
+$23,170/呎
 (26年-03月-09日)</t>
         </is>
       </c>

--- a/files/九龙-启德-柏蔚森 III.xlsx
+++ b/files/九龙-启德-柏蔚森 III.xlsx
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>7946000</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>20801</v>
+        <v>20856</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>7946000</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>20801</v>
+        <v>20856</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
@@ -18139,9 +18139,9 @@
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t>F | 382呎 (2房)
+          <t>F | 381呎 (2房)
 $795万
-$20,801/呎
+$20,856/呎
 (25年-11月-11日)</t>
         </is>
       </c>

--- a/files/九龙-启德-柏蔚森 III.xlsx
+++ b/files/九龙-启德-柏蔚森 III.xlsx
@@ -13038,7 +13038,7 @@
         </is>
       </c>
       <c r="E197" s="4" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>5982000</v>
       </c>
       <c r="I197" s="5" t="n">
-        <v>22745</v>
+        <v>22659</v>
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>5982000</v>
       </c>
       <c r="L197" s="5" t="n">
-        <v>22745</v>
+        <v>22659</v>
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
@@ -19168,9 +19168,9 @@
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>D | 263呎 (1房)
+          <t>D | 264呎 (1房)
 $598万
-$22,745/呎
+$22,659/呎
 (26年-07月-09日)</t>
         </is>
       </c>

--- a/files/九龙-启德-柏蔚森 III.xlsx
+++ b/files/九龙-启德-柏蔚森 III.xlsx
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>5107000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>19418</v>
+        <v>19345</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>5107000</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>19418</v>
+        <v>19345</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -17838,9 +17838,9 @@
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>D | 263呎 (1房)
+          <t>D | 264呎 (1房)
 $511万
-$19,418/呎
+$19,345/呎
 (24年-10月-25日)</t>
         </is>
       </c>
@@ -18775,7 +18775,7 @@
           <t>B | 382呎 (2房)
 $913万
 $23,911/呎
-(26年-09月-05日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">

--- a/files/九龙-启德-柏蔚森 III.xlsx
+++ b/files/九龙-启德-柏蔚森 III.xlsx
@@ -14774,7 +14774,7 @@
         </is>
       </c>
       <c r="E225" s="4" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>5545000</v>
       </c>
       <c r="I225" s="5" t="n">
-        <v>21245</v>
+        <v>21164</v>
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>5545000</v>
       </c>
       <c r="L225" s="5" t="n">
-        <v>21245</v>
+        <v>21164</v>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
@@ -19493,9 +19493,9 @@
       </c>
       <c r="J25" s="22" t="inlineStr">
         <is>
-          <t>J | 261呎 (1房)
+          <t>J | 262呎 (1房)
 $554万
-$21,245/呎
+$21,164/呎
 (26年-07月-16日)</t>
         </is>
       </c>

--- a/files/九龙-启德-柏蔚森 III.xlsx
+++ b/files/九龙-启德-柏蔚森 III.xlsx
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>9391000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>24584</v>
+        <v>24520</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>9391000</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>24584</v>
+        <v>24520</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>5107000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>19345</v>
+        <v>19418</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>5107000</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>19345</v>
+        <v>19418</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>8851000</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>23170</v>
+        <v>23110</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>8851000</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>23170</v>
+        <v>23110</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>7946000</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>20856</v>
+        <v>20801</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         <v>7946000</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>20856</v>
+        <v>20801</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>6959000</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>18217</v>
+        <v>18170</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>6959000</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>18217</v>
+        <v>18170</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>4772000</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>18076</v>
+        <v>18144</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>4772000</v>
       </c>
       <c r="L164" s="5" t="n">
-        <v>18076</v>
+        <v>18144</v>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         </is>
       </c>
       <c r="E197" s="4" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>5982000</v>
       </c>
       <c r="I197" s="5" t="n">
-        <v>22659</v>
+        <v>22745</v>
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>5982000</v>
       </c>
       <c r="L197" s="5" t="n">
-        <v>22659</v>
+        <v>22745</v>
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         </is>
       </c>
       <c r="E225" s="4" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>5545000</v>
       </c>
       <c r="I225" s="5" t="n">
-        <v>21164</v>
+        <v>21245</v>
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>5545000</v>
       </c>
       <c r="L225" s="5" t="n">
-        <v>21164</v>
+        <v>21245</v>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
@@ -17838,17 +17838,17 @@
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>D | 264呎 (1房)
+          <t>D | 263呎 (1房)
 $511万
-$19,345/呎
+$19,418/呎
 (24年-10月-25日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t>E | 382呎 (2房)
+          <t>E | 383呎 (2房)
 $939万
-$24,584/呎
+$24,520/呎
 (26年-06月-03日)</t>
         </is>
       </c>
@@ -18036,9 +18036,9 @@
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t>E | 382呎 (2房)
+          <t>E | 383呎 (2房)
 $885万
-$23,170/呎
+$23,110/呎
 (26年-03月-09日)</t>
         </is>
       </c>
@@ -18139,9 +18139,9 @@
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t>F | 381呎 (2房)
+          <t>F | 382呎 (2房)
 $795万
-$20,856/呎
+$20,801/呎
 (25年-11月-11日)</t>
         </is>
       </c>
@@ -18701,9 +18701,9 @@
       </c>
       <c r="F17" s="22" t="inlineStr">
         <is>
-          <t>E | 382呎 (2房)
+          <t>E | 383呎 (2房)
 $696万
-$18,217/呎
+$18,170/呎
 (24年-10月-23日)</t>
         </is>
       </c>
@@ -18883,9 +18883,9 @@
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>D | 264呎 (1房)
+          <t>D | 263呎 (1房)
 $477万
-$18,076/呎
+$18,144/呎
 (24年-09月-03日)</t>
         </is>
       </c>
@@ -19168,9 +19168,9 @@
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>D | 264呎 (1房)
+          <t>D | 263呎 (1房)
 $598万
-$22,659/呎
+$22,745/呎
 (26年-07月-09日)</t>
         </is>
       </c>
@@ -19493,9 +19493,9 @@
       </c>
       <c r="J25" s="22" t="inlineStr">
         <is>
-          <t>J | 262呎 (1房)
+          <t>J | 261呎 (1房)
 $554万
-$21,164/呎
+$21,245/呎
 (26年-07月-16日)</t>
         </is>
       </c>
